--- a/pareto_cpius/tabelas_cpi_macroitau.xlsx
+++ b/pareto_cpius/tabelas_cpi_macroitau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos gerais\Projetos-dev\python_projects\python_tools\pareto_cpius\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62DF2F3-B1FF-4193-A093-7CD1DC67B624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B4EE5E-6920-4EAF-B419-FBB0E7C713BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2592" yWindow="2268" windowWidth="10344" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mom sa" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>US CPI</t>
   </si>
@@ -74,6 +74,36 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  goods ex food &amp; energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  services ex. energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    core services ex-shelter plus lodging away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    core services ex-shelter</t>
+  </si>
+  <si>
+    <t>core cpi ex oer</t>
+  </si>
+  <si>
+    <t>cpi ex oer</t>
+  </si>
+  <si>
+    <t>core services ex rent of shelter, public transportation &amp; medical services</t>
+  </si>
+  <si>
+    <t>super super core</t>
+  </si>
+  <si>
+    <t>core services ex volatiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    core services ex-rents of shelter (ou ex rpr &amp; oer, powell super core)</t>
   </si>
 </sst>
 </file>
@@ -117,13 +147,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,24 +435,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -545,6 +580,492 @@
       <c r="M4">
         <v>-0.02</v>
       </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.21</v>
+      </c>
+      <c r="C5">
+        <v>0.22</v>
+      </c>
+      <c r="D5">
+        <v>0.2</v>
+      </c>
+      <c r="E5">
+        <v>0.03</v>
+      </c>
+      <c r="F5">
+        <v>0.03</v>
+      </c>
+      <c r="G5">
+        <v>0.03</v>
+      </c>
+      <c r="H5">
+        <v>0.04</v>
+      </c>
+      <c r="I5">
+        <v>0.08</v>
+      </c>
+      <c r="J5">
+        <v>0.11</v>
+      </c>
+      <c r="K5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L5">
+        <v>-0.11</v>
+      </c>
+      <c r="M5">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>0.35</v>
+      </c>
+      <c r="C6">
+        <v>0.32</v>
+      </c>
+      <c r="D6">
+        <v>0.23</v>
+      </c>
+      <c r="E6">
+        <v>0.1</v>
+      </c>
+      <c r="F6">
+        <v>0.1</v>
+      </c>
+      <c r="G6">
+        <v>0.27</v>
+      </c>
+      <c r="H6">
+        <v>0.39</v>
+      </c>
+      <c r="I6">
+        <v>0.27</v>
+      </c>
+      <c r="J6">
+        <v>0.23</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M6">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>0.46</v>
+      </c>
+      <c r="C7">
+        <v>0.31</v>
+      </c>
+      <c r="D7">
+        <v>0.31</v>
+      </c>
+      <c r="E7">
+        <v>0.05</v>
+      </c>
+      <c r="F7">
+        <v>0.05</v>
+      </c>
+      <c r="G7">
+        <v>0.23</v>
+      </c>
+      <c r="H7">
+        <v>0.59</v>
+      </c>
+      <c r="I7">
+        <v>0.35</v>
+      </c>
+      <c r="J7">
+        <v>0.18</v>
+      </c>
+      <c r="K7">
+        <v>0.45</v>
+      </c>
+      <c r="L7">
+        <v>0.27</v>
+      </c>
+      <c r="M7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.44</v>
+      </c>
+      <c r="C8">
+        <v>0.31</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="E8">
+        <v>0.05</v>
+      </c>
+      <c r="F8">
+        <v>0.05</v>
+      </c>
+      <c r="G8">
+        <v>0.22</v>
+      </c>
+      <c r="H8">
+        <v>0.59</v>
+      </c>
+      <c r="I8">
+        <v>0.35</v>
+      </c>
+      <c r="J8">
+        <v>0.17</v>
+      </c>
+      <c r="K8">
+        <v>0.46</v>
+      </c>
+      <c r="L8">
+        <v>0.27</v>
+      </c>
+      <c r="M8">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>0.52</v>
+      </c>
+      <c r="C9">
+        <v>0.21</v>
+      </c>
+      <c r="D9">
+        <v>0.27</v>
+      </c>
+      <c r="E9">
+        <v>0.08</v>
+      </c>
+      <c r="F9">
+        <v>0.08</v>
+      </c>
+      <c r="G9">
+        <v>0.12</v>
+      </c>
+      <c r="H9">
+        <v>0.63</v>
+      </c>
+      <c r="I9">
+        <v>0.32</v>
+      </c>
+      <c r="J9">
+        <v>0.17</v>
+      </c>
+      <c r="K9">
+        <v>0.35</v>
+      </c>
+      <c r="L9">
+        <v>0.26</v>
+      </c>
+      <c r="M9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0.12</v>
+      </c>
+      <c r="C10">
+        <v>0.42</v>
+      </c>
+      <c r="D10">
+        <v>0.22</v>
+      </c>
+      <c r="E10">
+        <v>0.04</v>
+      </c>
+      <c r="F10">
+        <v>0.04</v>
+      </c>
+      <c r="G10">
+        <v>0.66</v>
+      </c>
+      <c r="H10">
+        <v>0.19</v>
+      </c>
+      <c r="I10">
+        <v>0.39</v>
+      </c>
+      <c r="J10">
+        <v>-0.01</v>
+      </c>
+      <c r="K10">
+        <v>0.5</v>
+      </c>
+      <c r="L10">
+        <v>0.16</v>
+      </c>
+      <c r="M10">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>-0.62</v>
+      </c>
+      <c r="C11">
+        <v>0.69</v>
+      </c>
+      <c r="D11">
+        <v>1.43</v>
+      </c>
+      <c r="E11">
+        <v>0.7</v>
+      </c>
+      <c r="F11">
+        <v>0.7</v>
+      </c>
+      <c r="G11">
+        <v>0.34</v>
+      </c>
+      <c r="H11">
+        <v>-1.47</v>
+      </c>
+      <c r="I11">
+        <v>0.63</v>
+      </c>
+      <c r="J11">
+        <v>10.87</v>
+      </c>
+      <c r="K11">
+        <v>3.81</v>
+      </c>
+      <c r="L11">
+        <v>3.88</v>
+      </c>
+      <c r="M11">
+        <v>-5.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>0.33</v>
+      </c>
+      <c r="C12">
+        <v>0.3</v>
+      </c>
+      <c r="D12">
+        <v>0.25</v>
+      </c>
+      <c r="E12">
+        <v>0.05</v>
+      </c>
+      <c r="F12">
+        <v>0.08</v>
+      </c>
+      <c r="G12">
+        <v>0.2</v>
+      </c>
+      <c r="H12">
+        <v>0.33</v>
+      </c>
+      <c r="I12">
+        <v>0.21</v>
+      </c>
+      <c r="J12">
+        <v>0.16</v>
+      </c>
+      <c r="K12">
+        <v>0.31</v>
+      </c>
+      <c r="L12">
+        <v>0.17</v>
+      </c>
+      <c r="M12">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>0.21</v>
+      </c>
+      <c r="C13">
+        <v>0.35</v>
+      </c>
+      <c r="D13">
+        <v>0.34</v>
+      </c>
+      <c r="E13">
+        <v>0.01</v>
+      </c>
+      <c r="F13">
+        <v>0.22</v>
+      </c>
+      <c r="G13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H13">
+        <v>0.15</v>
+      </c>
+      <c r="I13">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J13">
+        <v>1.06</v>
+      </c>
+      <c r="K13">
+        <v>0.68</v>
+      </c>
+      <c r="L13">
+        <v>0.53</v>
+      </c>
+      <c r="M13">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>0.27</v>
+      </c>
+      <c r="C14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D14">
+        <v>0.2</v>
+      </c>
+      <c r="F14">
+        <v>0.46</v>
+      </c>
+      <c r="G14">
+        <v>-0.27</v>
+      </c>
+      <c r="H14">
+        <v>0.48</v>
+      </c>
+      <c r="I14">
+        <v>0.24</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="K14">
+        <v>0.32</v>
+      </c>
+      <c r="L14">
+        <v>0.13</v>
+      </c>
+      <c r="M14">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>0.31</v>
+      </c>
+      <c r="C15">
+        <v>0.12</v>
+      </c>
+      <c r="D15">
+        <v>0.22</v>
+      </c>
+      <c r="F15">
+        <v>0.4</v>
+      </c>
+      <c r="G15">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="H15">
+        <v>0.43</v>
+      </c>
+      <c r="I15">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J15">
+        <v>0.1</v>
+      </c>
+      <c r="K15">
+        <v>0.33</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>0.25</v>
+      </c>
+      <c r="C16">
+        <v>0.3</v>
+      </c>
+      <c r="D16">
+        <v>0.2</v>
+      </c>
+      <c r="F16">
+        <v>0.3</v>
+      </c>
+      <c r="G16">
+        <v>0.2</v>
+      </c>
+      <c r="H16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I16">
+        <v>0.2</v>
+      </c>
+      <c r="J16">
+        <v>0.21</v>
+      </c>
+      <c r="K16">
+        <v>0.52</v>
+      </c>
+      <c r="L16">
+        <v>0.21</v>
+      </c>
+      <c r="M16">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -556,207 +1077,362 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04037CA-7BA9-40AD-A2BC-DE3BB3784AEF}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
+        <v>45962</v>
+      </c>
+      <c r="C2" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46082</v>
+      </c>
+      <c r="G2" s="1">
         <v>46113</v>
       </c>
-      <c r="C2" s="1">
+      <c r="H2" s="1">
         <v>46143</v>
       </c>
-      <c r="D2" s="1">
+      <c r="I2" s="1">
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="G3">
         <v>3.81</v>
       </c>
-      <c r="C3">
+      <c r="H3">
         <v>4.25</v>
       </c>
-      <c r="D3">
+      <c r="I3">
         <v>3.53</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
         <v>2.75</v>
       </c>
-      <c r="C4">
+      <c r="H4">
         <v>2.85</v>
       </c>
-      <c r="D4">
+      <c r="I4">
         <v>2.59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="G5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C5">
+      <c r="H5">
         <v>1.06</v>
       </c>
-      <c r="D5">
+      <c r="I5">
         <v>0.82</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="G6">
         <v>3.27</v>
       </c>
-      <c r="C6">
+      <c r="H6">
         <v>3.42</v>
       </c>
-      <c r="D6">
+      <c r="I6">
         <v>3.16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="G7">
         <v>3.38</v>
       </c>
-      <c r="C7">
+      <c r="H7">
         <v>3.66</v>
       </c>
-      <c r="D7">
+      <c r="I7">
         <v>3.17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="G8">
         <v>3.29</v>
       </c>
-      <c r="C8">
+      <c r="H8">
         <v>3.58</v>
       </c>
-      <c r="D8">
+      <c r="I8">
         <v>3.1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="G9">
         <v>3.22</v>
       </c>
-      <c r="C9">
+      <c r="H9">
         <v>3.49</v>
       </c>
-      <c r="D9">
+      <c r="I9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="G10">
         <v>3.18</v>
       </c>
-      <c r="C10">
+      <c r="H10">
         <v>3.08</v>
       </c>
-      <c r="D10">
+      <c r="I10">
         <v>3.01</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="G11">
         <v>17.87</v>
       </c>
-      <c r="C11">
+      <c r="H11">
         <v>23.54</v>
       </c>
-      <c r="D11">
+      <c r="I11">
         <v>15.7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="G12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="H12" t="s">
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="I12">
         <v>2.36</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="G13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
+      <c r="H13" t="s">
         <v>15</v>
       </c>
-      <c r="D13">
+      <c r="I13">
         <v>2.67</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="G14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
+      <c r="H14" t="s">
         <v>15</v>
       </c>
-      <c r="D14">
+      <c r="I14">
         <v>2.61</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="3"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>3.64</v>
+      </c>
+      <c r="C15">
+        <v>3.16</v>
+      </c>
+      <c r="D15">
+        <v>3.52</v>
+      </c>
+      <c r="E15">
+        <v>2.91</v>
+      </c>
+      <c r="F15">
+        <v>2.4</v>
+      </c>
+      <c r="G15">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="H15">
+        <v>2.42</v>
+      </c>
+      <c r="I15">
+        <v>2.11</v>
+      </c>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>3.31</v>
+      </c>
+      <c r="C16">
+        <v>3.28</v>
+      </c>
+      <c r="D16">
+        <v>3.43</v>
+      </c>
+      <c r="E16">
+        <v>3.13</v>
+      </c>
+      <c r="F16">
+        <v>3.03</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3.26</v>
+      </c>
+      <c r="H16">
+        <v>3.23</v>
+      </c>
+      <c r="I16">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>3.37</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>3.29</v>
+      </c>
+      <c r="E17">
+        <v>2.74</v>
+      </c>
+      <c r="F17">
+        <v>2.35</v>
+      </c>
+      <c r="G17">
+        <v>2.44</v>
+      </c>
+      <c r="H17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="I17">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C18">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="D18">
+        <v>2.16</v>
+      </c>
+      <c r="E18">
+        <v>2.13</v>
+      </c>
+      <c r="F18">
+        <v>2.37</v>
+      </c>
+      <c r="G18">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="H18">
+        <v>2.65</v>
+      </c>
+      <c r="I18">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>2.52</v>
+      </c>
+      <c r="C19">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="D19">
+        <v>2.1</v>
+      </c>
+      <c r="E19">
+        <v>2.16</v>
+      </c>
+      <c r="F19">
+        <v>3.31</v>
+      </c>
+      <c r="G19">
+        <v>3.98</v>
+      </c>
+      <c r="H19">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="I19">
+        <v>3.63</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
